--- a/db/sctype.brain.xlsx
+++ b/db/sctype.brain.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/2.celltypeAnno/public_version/cte.v0.3.Nature/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/1._markerDatabase/_celltypeMarkers/publicDB/ScType/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0B816E-04A4-4E48-9261-2478BE529A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88C68D4-BE9F-9041-8739-CE0A92EEF613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25140" windowHeight="19040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="32320" windowHeight="17700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -28,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="235">
   <si>
     <t>tissueType</t>
   </si>
@@ -39,6 +36,9 @@
     <t>geneSymbolmore1</t>
   </si>
   <si>
+    <t>Pericytes</t>
+  </si>
+  <si>
     <t>Endothelial cells</t>
   </si>
   <si>
@@ -174,6 +174,9 @@
     <t>Mast cells</t>
   </si>
   <si>
+    <t>Monocytes</t>
+  </si>
+  <si>
     <t>Immune system</t>
   </si>
   <si>
@@ -348,9 +351,6 @@
     <t>CD203c,CD15,CD11b,CD63,CD66b,CD123,CD16,CD33,CD117,CD45,Fc-epsilon RI-alpha,CD125,CD13,CD14,CD25,CD44,CD69,CD9,HLA-DR,CCR3,CD116,CD11c,CD193,CD24,CD32,CD43,CXCL8,FCGR3B,MNDA,SIGLEC8,AZU1,MPO,CTSG,LYZ</t>
   </si>
   <si>
-    <t>γδ-T cells</t>
-  </si>
-  <si>
     <t>ISG expressing immune cells</t>
   </si>
   <si>
@@ -360,10 +360,7 @@
     <t>Cancer cells</t>
   </si>
   <si>
-    <t>CD44,MBTPS2,PARP1</t>
-  </si>
-  <si>
-    <t>FUT4,MSI1,NES,PROM1,SOX2,THY1</t>
+    <t>CD44,EPCAM,ERBB2,FOLH1,KRT18,PROM1</t>
   </si>
   <si>
     <t>CD8,CD2,CD3D,CD3E,CD3G,CD3Z,CD45RA,CD62L,CD27,CD127,FOXP3,CCR7,CD45,CD8A,CD8B,CCR6,CD11b,CD30,CD6,CTLA4,IL2RA,GZMB,PTPRC,SELL,CCR7,GNLY,Trac,Ltb,Cd52,Trbc2,Shisa5,Lck,Thy1,Dapl1</t>
@@ -426,9 +423,6 @@
     <t>Plasma B</t>
   </si>
   <si>
-    <t>γδ-T</t>
-  </si>
-  <si>
     <t>CD8+ NKT</t>
   </si>
   <si>
@@ -441,18 +435,12 @@
     <t>Mast</t>
   </si>
   <si>
-    <t>MΦ</t>
-  </si>
-  <si>
     <t>MKs</t>
   </si>
   <si>
     <t>ECs</t>
   </si>
   <si>
-    <t>Es</t>
-  </si>
-  <si>
     <t>HSC/MPP</t>
   </si>
   <si>
@@ -495,9 +483,6 @@
     <t>Non myelinating Schwann</t>
   </si>
   <si>
-    <t>Oligodendrocyte precursor</t>
-  </si>
-  <si>
     <t>Radial glial</t>
   </si>
   <si>
@@ -532,13 +517,226 @@
   </si>
   <si>
     <t>CD27,IgD,CD38,CD24,CD20,MS4A1,PTPRC,PAX5,CD24,CD38,CD79A,JCHAIN,SSR4,FKBP11,SEC11C,DERL3,PRDX4,IGLL5,CD79B,TCL1A,IGLL5,HLA-DQA1,HLA-DQB1,CD138,CD38,VPREB3,IGLL5</t>
+  </si>
+  <si>
+    <t>(Pro-) Subiculum</t>
+  </si>
+  <si>
+    <t>Activated Microglia</t>
+  </si>
+  <si>
+    <t>Agt Astrocytes</t>
+  </si>
+  <si>
+    <t>CA1-dorsal Principal</t>
+  </si>
+  <si>
+    <t>CA1-ventr Principal</t>
+  </si>
+  <si>
+    <t>CA2 Principal</t>
+  </si>
+  <si>
+    <t>CA3-dorsal Principal</t>
+  </si>
+  <si>
+    <t>CA3-ventr Principal</t>
+  </si>
+  <si>
+    <t>Cajal-Retzius</t>
+  </si>
+  <si>
+    <t>Choroid plexus</t>
+  </si>
+  <si>
+    <t>Dentate Hilum (CA4)</t>
+  </si>
+  <si>
+    <t>Ependymal</t>
+  </si>
+  <si>
+    <t>Fibroblast-like</t>
+  </si>
+  <si>
+    <t>Gfap++ Astrocytes</t>
+  </si>
+  <si>
+    <t>Immature Granule Cells (DG)</t>
+  </si>
+  <si>
+    <t>GABA</t>
+  </si>
+  <si>
+    <t>Mature Granule Cells (DG)</t>
+  </si>
+  <si>
+    <t>Neurogenesis</t>
+  </si>
+  <si>
+    <t>Polydendrocytes</t>
+  </si>
+  <si>
+    <t>Resident Microglia</t>
+  </si>
+  <si>
+    <t>Smooth Muscle</t>
+  </si>
+  <si>
+    <t>Unc13c Astrocytes</t>
+  </si>
+  <si>
+    <t>VGLUT2 Neurons</t>
+  </si>
+  <si>
+    <t>Hippocampus</t>
+  </si>
+  <si>
+    <t>LIPM,NPSR1,RAB38,FN1,KLHL1,ADAMTS2,NTS,STAC,TLE4,RXFP1</t>
+  </si>
+  <si>
+    <t>DOCK8,FYB,CSF3R,IKZF1,TMEM119,CCL4,ADAP2,OLFML3,RUNX1,SELPLG,DOCK2,FYB,SLCO2B1,ABCA9,RASGRP3,CX3CR1,LAIR1,UNC93B1,LAPTM5,CD53,P2RY12,ENTPD1,ITGB5,LY86,APBB1IP,HPGDS,ARHGAP22,CSF1R,P3H2,FCGR3,B4GALT1,ITGA9</t>
+  </si>
+  <si>
+    <t>FAM20A,EZR,CMTM5,BMPR1B,SDC4,SOX9,ACSBG1,MLC1,S100A1,F3,PRDM16,AQP4,ID4,HSD11B1,SLC6A11,RORB,ACOT11,GLI3,AGT,SLC39A12,ACSBG1</t>
+  </si>
+  <si>
+    <t>FAM20A,EZR,BMPR1B,SOX9,ACSBG1,F3,PRDM16,AQP4,ID4,SLC6A11,RORB,ACOT11,GLI3,SLC39A12,ACSBG1</t>
+  </si>
+  <si>
+    <t>RGS14,SYT1,GRIN2A,GREM1,EGFL6,STRIP2,SLC9A2,LEFTY1,NPR3,GM10754,KLK8,WFS1,FIBCD1,LEFTY1,STAC,FIBCD1,HTR1B,SPINK8,STAC,SATB2,C1QL3</t>
+  </si>
+  <si>
+    <t>RGS14,SYT1,GRIN2A,FIBCD1,DCN,DIO3,APELA,DLK1,ARHGAP36,LEFTY1,GPR101,GPC3,SATB2,C1QL3</t>
+  </si>
+  <si>
+    <t>VIT,AMIGO2,RGS14,DUSP5,STRIP2,MAP3K15,PCP4,HS3ST4,SYCE2,NTSR2,SOSTDC1</t>
+  </si>
+  <si>
+    <t>CLDN22,CD109,IYD,IFI203,PRSS35,CYP26B1,CPNE9,CYP26B1,HS3ST4,HOMER3,BOK,PRKCD</t>
+  </si>
+  <si>
+    <t>NKD2,HS3ST4,BOK,COCH,VGLL3,BACE2,HOMER3</t>
+  </si>
+  <si>
+    <t>EBF3,TRP73,RELN,NHLH2,CACNA2D2,EYA2,LHX1OS</t>
+  </si>
+  <si>
+    <t>TMEM72,WFDC2,FOLR1,OTX2OS1,CLDN2,OTX2,CLIC6,KCNE2,SLC13A4</t>
+  </si>
+  <si>
+    <t>CALB2,GLP1R,GRM8,DRD2,PRRX1,GAL,CHGA,CNTN6,VAT1,RAC3,AJAP1,GLRA3,ONECUT2,CPNE9,HPCAL1,DRD2,RBPMS2,CPNE9,C1QL3</t>
+  </si>
+  <si>
+    <t>ESAM,CDH5,LY6A,USHBP1,KANK3,CMTM8,FN1,PROM1,PLTP,OCLN,ABCB1A,EGFL7,CGNL1,FOXQ1,KLF4,FGD5,ID1,PGLYRP1,PAQR5,LTBP4,KLF2,GIMAP6,ATP10A,TEK,PRKCH,CYYR1,ABCC4,CLEC2D,EBF1,PTPRB,NOS3,PODXL,CLIC5,LEF1,SLC2A1,AFAP1L1,SLCO1A4,ROBO4,TIE1,MECOM,ZFP366,CLDN5,ENG,SOX18,HMCN1,HSPA12B,KITL,NOSTRIN,VWA1,FLT1,PECAM1,ABCG2</t>
+  </si>
+  <si>
+    <t>FOXJ1,SNTN,KRT15,TMEM212,DYNLRB2,CFAP126,CCDC146,CCDC153,AK7,SPAG17,ENKUR,SPAG17,SPA17,MLF1,RIIAD1,SPEF2,MEIG1</t>
+  </si>
+  <si>
+    <t>SLC22A6,ISLR,LAMA1,FMOD,BMP6,LAMC3,COL13A1,LUM,GJB2,GPR182,COL4A6,OSR1,SLC6A13,COL1A1,BMP7,GXYLT2,COL4A5,CYP1B1,SLC13A3,MPZL2,ENPP1,COL1A2,CPED1,EYA2,AOX3,ARHGAP28,NUPR1,COL3A1,SLC13A4,RANBP3L,PDGFRA,PTGDS,SLC13A4</t>
+  </si>
+  <si>
+    <t>FAM20A,EZR,BMPR1B,SOX9,ACSBG1,FABP7,GFAP,AQP4,ID4,SLC6A11,RORB,ACOT11,MYOC,SLC39A12,ACSBG1,FXYD1</t>
+  </si>
+  <si>
+    <t>PCP4,ARSJ,CENPA,GSG1L,SV2C,PROX1,STXBP6,RFX3,PRTG,C1QL3,NTF3,ARSJ,SEMA5A,ZFHX2OS,KCNK1,STXBP6,SOX11,GM20687,NEUROD1</t>
+  </si>
+  <si>
+    <t>SV2C,GAD2,DLX1,SLC32A1,COL19A1,LHX6,CORT,GAD1,PVALB,SST,VGAT,SLC6A1,ALK,CNTNAP4,KCNMB2,CNTNAP3,DLX6OS1,DLX1AS</t>
+  </si>
+  <si>
+    <t>PCP4,PROX1,CALB1,FAM163B,C1QL3,DSP,LCT,NTF3,GMNC,ARSJ,NPNT,CCNJL,DSP,SEMA5A,KCNK1,STXBP6,GFRA2,NTF3</t>
+  </si>
+  <si>
+    <t>TOP2A,IGFBPL1,HMGB2,ASCL1,SOX4,SOX11,NEUROD1</t>
+  </si>
+  <si>
+    <t>TTYH2,CPM,CARHSP1,EFHD1,CRYAB,OPALIN,TMEM88B,MOG,PLEKHH1,CLDN11,TNFAIP6,TMEM63A,GALNT6,CYP2J12,UGT8A,PHLDB1,PPP1R14A,PTGDS,MAG,CCP110,ANLN,MAL,CNP,QDPR,HHIP,IL33,FA2H,MOBP,TNNI1</t>
+  </si>
+  <si>
+    <t>KCNJ8,ECM2,LIMD1,ITGA1,IFITM1,NBL1,CSPG4,PDE5A,VTN,PLXDC1,IGFBP7,IL34,ADAP2,CYSLTR2,SLC6A20A,GGT5,ABCC9,HIGD1B,ATP13A5,EGFLAM,AIRN,ZIC1,NDUFA4L2,PHLDB2,DCDC2A,MYO1B,SLC16A12,COLEC12,ATP2A3,FOXD1,ART3,GPER1,RGS5,SNTB1,NID1,PDGFRB,NOTCH3,ANO1,RBPMS,NID1,TBX3OS1,GM13861,EBF1</t>
+  </si>
+  <si>
+    <t>PPFIBP1,B3GAT2,NTN1,CALCRL,PRKCQ,STK32A,ARHGAP24,CSPG4,RLBP1,LHFPL3,CAR8,SH3BP4,ITGA9,GM4876,AFAP1L2,NEU4,CACNG4,SEMA3D,C1QL1,SHC4,MEGF11,SEMA5B,ABTB2,EMID1,KCNH8,PDGFRA,TMEM163</t>
+  </si>
+  <si>
+    <t>AOAH,CTSC,MS4A7,MRC1,F13A1,CLEC4A1,DOCK8,FCGR2B,CYBB,CD86,BANK1,MS4A6D,PF4,LYZ2,CFH,MS4A6C,TGFBI,FYB,RUNX1,SLCO2B1,ABCA9,HPGDS,CSF1R,B4GALT1,IFI203</t>
+  </si>
+  <si>
+    <t>MYLK,MYL9,MYO1E,ARHGAP6,RHOJ,C1QTNF7,LIMD1,LTBP1,PDE3A,GM13861,RNF152,FLNA,DES,AOC3,ADAMTS1,ARHGAP10,RASGRP2,MYH11,BGN,SNTB1,SLC38A11,RBPMS,FILIP1L,EBF1,TNS1,EHD2,WNT5B,FOXC1,MAP3K7CL,EDNRA,MYOCD,ANO1,FILIP1,GPER1,AHNAK,NET1,ACTA2,MCAM,NTN4,MUSTN1,PLN,NOTCH3,TAGLN,MYL9</t>
+  </si>
+  <si>
+    <t>FAM20A,EZR,PHKG1,BMPR1B,FGFR3,SOX9,ACSBG1,NWD1,F3,PRDM16,AQP4,SLC6A11,ST3GAL4,RORB,ACOT11,GLI3,GRIN2C,UNC13,SLC39A12,ACSBG1</t>
+  </si>
+  <si>
+    <t>NPSR1,GSG1L,GRM4,RXFP1,CHRM2,NREP</t>
+  </si>
+  <si>
+    <t>Gamma-delta T cells</t>
+  </si>
+  <si>
+    <t>Gamma-delta T</t>
+  </si>
+  <si>
+    <t>EPCs</t>
+  </si>
+  <si>
+    <t>Prosubiculum</t>
+  </si>
+  <si>
+    <t>Microglia</t>
+  </si>
+  <si>
+    <t>Neurons</t>
+  </si>
+  <si>
+    <t>shortName2</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Subclass</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Subregion</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Hipp-CA1</t>
+  </si>
+  <si>
+    <t>Hipp-CA2</t>
+  </si>
+  <si>
+    <t>Hipp-CA3</t>
+  </si>
+  <si>
+    <t>Hipp-CA4</t>
+  </si>
+  <si>
+    <t>Hipp-DG</t>
+  </si>
+  <si>
+    <t>OPC</t>
+  </si>
+  <si>
+    <t>MSI1,NES,PROM1,SOX2,THY1</t>
+  </si>
+  <si>
+    <t>ScType</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -547,46 +745,31 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4D5156"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF333333"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF4D5156"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -609,28 +792,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,180 +1123,229 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E86"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K250"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="214.6640625" customWidth="1"/>
-    <col min="4" max="4" width="27.1640625" customWidth="1"/>
-    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="214.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.83203125" style="1"/>
+    <col min="9" max="9" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="K3" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="K4" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="K5" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="K6" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>117</v>
@@ -1128,15 +1354,18 @@
         <v>125</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>118</v>
@@ -1145,15 +1374,18 @@
         <v>125</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>106</v>
+        <v>215</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>113</v>
@@ -1162,840 +1394,2549 @@
         <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="K17" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>122</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>124</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="2" t="s">
+      <c r="K45" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="4" t="s">
+      <c r="K58" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="4" t="s">
+      <c r="I61" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="4"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="6"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="4"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="6"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="4"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="6"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="4"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="6"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="4"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="6"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="4"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="6"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="4"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="6"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="4"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="6"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="4"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="6"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="4"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="6"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="4"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="6"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="6"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="4"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="6"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="4"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="6"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="6"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="4"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="6"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="6"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="4"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="6"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="4"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="6"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="4"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="6"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="6"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" s="4"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="6"/>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="6"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="6"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="4"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="6"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="4"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="6"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="4"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="6"/>
+      <c r="C80" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="4"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" s="2"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182" s="2"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A187" s="2"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188" s="2"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189" s="2"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A190" s="2"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A191" s="2"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="2"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A192" s="2"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A193" s="2"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A194" s="2"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A195" s="2"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A196" s="2"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="2"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A197" s="2"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198" s="2"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A199" s="2"/>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A200" s="2"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201" s="2"/>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A202" s="2"/>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A203" s="2"/>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A204" s="2"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A205" s="2"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A206" s="2"/>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A208" s="2"/>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A209" s="2"/>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
+      <c r="E209" s="2"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A210" s="2"/>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="2"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A211" s="2"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+      <c r="E211" s="2"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A212" s="2"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A225" s="2"/>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A226" s="2"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A227" s="2"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A228" s="2"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+      <c r="E228" s="2"/>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A229" s="2"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
+      <c r="E229" s="2"/>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A230" s="2"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+      <c r="E230" s="2"/>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A231" s="2"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="2"/>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A233" s="2"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A234" s="2"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A238" s="2"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A242" s="2"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E250">
+    <sortCondition ref="A36:A250"/>
+  </sortState>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/db/sctype.brain.xlsx
+++ b/db/sctype.brain.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/1._markerDatabase/_celltypeMarkers/publicDB/ScType/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/2.celltypeAnno/public_version/cte.v0.3.2/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88C68D4-BE9F-9041-8739-CE0A92EEF613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A4B57D-1D00-334D-9757-82ADF3E81410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="32320" windowHeight="17700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="232">
   <si>
     <t>tissueType</t>
   </si>
@@ -219,9 +220,6 @@
     <t>Progenitor cells</t>
   </si>
   <si>
-    <t>Cancer stem cells</t>
-  </si>
-  <si>
     <t>Natural killer  cells</t>
   </si>
   <si>
@@ -462,9 +460,6 @@
     <t>Microglial</t>
   </si>
   <si>
-    <t>CSCs</t>
-  </si>
-  <si>
     <t>Cancer</t>
   </si>
   <si>
@@ -724,9 +719,6 @@
   </si>
   <si>
     <t>OPC</t>
-  </si>
-  <si>
-    <t>MSI1,NES,PROM1,SOX2,THY1</t>
   </si>
   <si>
     <t>ScType</t>
@@ -1123,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K250"/>
+  <dimension ref="A1:K240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1148,28 +1140,28 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1177,17 +1169,17 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1195,17 +1187,17 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1213,17 +1205,17 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1234,14 +1226,14 @@
         <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1252,16 +1244,16 @@
         <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1269,19 +1261,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1289,19 +1281,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1312,14 +1304,14 @@
         <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1327,17 +1319,17 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1345,19 +1337,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1365,19 +1357,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1385,19 +1377,19 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1408,14 +1400,14 @@
         <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -1423,17 +1415,17 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -1441,17 +1433,17 @@
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -1459,19 +1451,19 @@
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -1482,14 +1474,14 @@
         <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
         <v>52</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -1500,14 +1492,14 @@
         <v>56</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -1518,14 +1510,14 @@
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -1536,14 +1528,14 @@
         <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -1554,19 +1546,19 @@
         <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -1577,19 +1569,19 @@
         <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -1597,22 +1589,22 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -1623,16 +1615,16 @@
         <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -1640,17 +1632,17 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -1658,17 +1650,17 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -1679,14 +1671,14 @@
         <v>53</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -1694,19 +1686,19 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -1717,14 +1709,14 @@
         <v>63</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -1732,17 +1724,17 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -1750,17 +1742,17 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -1771,14 +1763,14 @@
         <v>54</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -1786,17 +1778,17 @@
         <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -1804,17 +1796,17 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -1832,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -1850,7 +1842,7 @@
         <v>8</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -1868,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -1883,10 +1875,10 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -1904,7 +1896,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -1922,7 +1914,7 @@
         <v>15</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -1940,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -1951,14 +1943,14 @@
         <v>19</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
         <v>50</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -1976,7 +1968,7 @@
         <v>20</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -1991,10 +1983,10 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -2009,10 +2001,10 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -2027,10 +2019,10 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2045,10 +2037,10 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -2066,7 +2058,7 @@
         <v>30</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -2081,10 +2073,10 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -2099,10 +2091,10 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -2117,10 +2109,10 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -2138,7 +2130,7 @@
         <v>38</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -2153,10 +2145,10 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -2171,10 +2163,10 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -2192,7 +2184,7 @@
         <v>44</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -2210,7 +2202,7 @@
         <v>46</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -2218,17 +2210,19 @@
         <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D58" s="2"/>
+        <v>187</v>
+      </c>
       <c r="E58" s="2" t="s">
-        <v>145</v>
+        <v>217</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -2242,13 +2236,13 @@
         <v>188</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>218</v>
+        <v>6</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -2256,19 +2250,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>189</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>219</v>
+        <v>6</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
@@ -2276,19 +2270,19 @@
         <v>5</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -2296,19 +2290,19 @@
         <v>5</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -2316,19 +2310,19 @@
         <v>5</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -2336,19 +2330,19 @@
         <v>5</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
@@ -2356,19 +2350,19 @@
         <v>5</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
@@ -2376,19 +2370,19 @@
         <v>5</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>229</v>
+        <v>6</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
@@ -2396,19 +2390,19 @@
         <v>5</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
@@ -2416,19 +2410,19 @@
         <v>5</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
@@ -2436,19 +2430,19 @@
         <v>5</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>173</v>
+        <v>38</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>173</v>
+        <v>38</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
@@ -2456,19 +2450,19 @@
         <v>5</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>174</v>
+        <v>3</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>230</v>
+        <v>3</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -2476,19 +2470,19 @@
         <v>5</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -2496,19 +2490,19 @@
         <v>5</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
@@ -2516,19 +2510,19 @@
         <v>5</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -2536,19 +2530,19 @@
         <v>5</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -2556,336 +2550,206 @@
         <v>5</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>234</v>
-      </c>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>234</v>
-      </c>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>234</v>
-      </c>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="5"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="C92" s="3"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
+      <c r="C93" s="3"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
+      <c r="C95" s="3"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
+      <c r="C96" s="3"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="C97" s="3"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
+      <c r="C98" s="3"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
+      <c r="C99" s="3"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
+      <c r="C100" s="3"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
+      <c r="C101" s="3"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
     </row>
@@ -2906,9 +2770,9 @@
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
+      <c r="C104" s="3"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
+      <c r="E104" s="4"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
@@ -2927,7 +2791,7 @@
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
-      <c r="C107" s="3"/>
+      <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
     </row>
@@ -2941,56 +2805,56 @@
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
-      <c r="C109" s="3"/>
+      <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
-      <c r="C110" s="3"/>
+      <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
-      <c r="C111" s="3"/>
+      <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
-      <c r="C112" s="3"/>
+      <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
-      <c r="C113" s="3"/>
+      <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
-      <c r="C114" s="3"/>
+      <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="4"/>
+      <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
-      <c r="C115" s="3"/>
+      <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
-      <c r="C116" s="3"/>
+      <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
     </row>
@@ -3004,7 +2868,7 @@
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
-      <c r="C118" s="3"/>
+      <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
     </row>
@@ -3862,82 +3726,202 @@
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A241" s="2"/>
-      <c r="B241" s="2"/>
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A242" s="2"/>
-      <c r="B242" s="2"/>
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A243" s="2"/>
-      <c r="B243" s="2"/>
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A244" s="2"/>
-      <c r="B244" s="2"/>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" s="2"/>
-      <c r="B245" s="2"/>
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A246" s="2"/>
-      <c r="B246" s="2"/>
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247" s="2"/>
-      <c r="B247" s="2"/>
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248" s="2"/>
-      <c r="B248" s="2"/>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A249" s="2"/>
-      <c r="B249" s="2"/>
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A250" s="2"/>
-      <c r="B250" s="2"/>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E250">
-    <sortCondition ref="A36:A250"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E240">
+    <sortCondition ref="A36:A240"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D0E990-649A-C44A-8355-B01009430605}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/db/sctype.brain.xlsx
+++ b/db/sctype.brain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/2.celltypeAnno/public_version/cte.v0.3.2/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A4B57D-1D00-334D-9757-82ADF3E81410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D32E75-2E51-1F48-B0CF-AD76095E5BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="32320" windowHeight="17700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="229">
   <si>
     <t>tissueType</t>
   </si>
@@ -355,12 +355,6 @@
     <t>IFIT1,IFIT2,IFIT3,IFIT5,ISG15,CCL3,CCL4,CCL3L3,RSAD2,OASL,CXCL10,IFI15,ISG20</t>
   </si>
   <si>
-    <t>Cancer cells</t>
-  </si>
-  <si>
-    <t>CD44,EPCAM,ERBB2,FOLH1,KRT18,PROM1</t>
-  </si>
-  <si>
     <t>CD8,CD2,CD3D,CD3E,CD3G,CD3Z,CD45RA,CD62L,CD27,CD127,FOXP3,CCR7,CD45,CD8A,CD8B,CCR6,CD11b,CD30,CD6,CTLA4,IL2RA,GZMB,PTPRC,SELL,CCR7,GNLY,Trac,Ltb,Cd52,Trbc2,Shisa5,Lck,Thy1,Dapl1</t>
   </si>
   <si>
@@ -458,9 +452,6 @@
   </si>
   <si>
     <t>Microglial</t>
-  </si>
-  <si>
-    <t>Cancer</t>
   </si>
   <si>
     <t>Myelinating Schwann</t>
@@ -1115,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K240"/>
+  <dimension ref="A1:K239"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1143,25 +1134,25 @@
         <v>73</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1176,10 +1167,10 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1194,10 +1185,10 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1212,10 +1203,10 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1230,10 +1221,10 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1244,16 +1235,16 @@
         <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1264,16 +1255,16 @@
         <v>80</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1284,16 +1275,16 @@
         <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1304,14 +1295,14 @@
         <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1322,14 +1313,14 @@
         <v>81</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1340,16 +1331,16 @@
         <v>82</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1360,16 +1351,16 @@
         <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1377,19 +1368,19 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1407,7 +1398,7 @@
         <v>58</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -1422,10 +1413,10 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -1440,10 +1431,10 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -1460,10 +1451,10 @@
         <v>101</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -1481,7 +1472,7 @@
         <v>52</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -1492,14 +1483,14 @@
         <v>56</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -1517,7 +1508,7 @@
         <v>51</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -1532,10 +1523,10 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -1546,7 +1537,7 @@
         <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>99</v>
@@ -1555,10 +1546,10 @@
         <v>49</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -1569,7 +1560,7 @@
         <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>65</v>
@@ -1578,10 +1569,10 @@
         <v>49</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -1592,7 +1583,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>65</v>
@@ -1601,10 +1592,10 @@
         <v>49</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -1615,7 +1606,7 @@
         <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>65</v>
@@ -1624,7 +1615,7 @@
         <v>55</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -1639,10 +1630,10 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -1657,10 +1648,10 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -1675,10 +1666,10 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -1695,10 +1686,10 @@
         <v>77</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -1713,10 +1704,10 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -1731,10 +1722,10 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -1749,10 +1740,10 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -1767,10 +1758,10 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -1785,10 +1776,10 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -1796,17 +1787,17 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -1814,17 +1805,17 @@
         <v>5</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -1832,17 +1823,17 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -1850,17 +1841,17 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -1868,17 +1859,17 @@
         <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -1886,17 +1877,17 @@
         <v>5</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -1904,17 +1895,17 @@
         <v>5</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -1922,17 +1913,17 @@
         <v>5</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -1940,17 +1931,17 @@
         <v>5</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -1958,17 +1949,17 @@
         <v>5</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -1976,17 +1967,17 @@
         <v>5</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -1994,17 +1985,17 @@
         <v>5</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -2012,17 +2003,17 @@
         <v>5</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2030,17 +2021,17 @@
         <v>5</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>147</v>
+        <v>30</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -2048,17 +2039,17 @@
         <v>5</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -2066,17 +2057,17 @@
         <v>5</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -2084,17 +2075,17 @@
         <v>5</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="s">
-        <v>149</v>
+        <v>227</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -2102,17 +2093,17 @@
         <v>5</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="s">
-        <v>230</v>
+        <v>38</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -2120,17 +2111,17 @@
         <v>5</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -2138,17 +2129,17 @@
         <v>5</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -2156,17 +2147,17 @@
         <v>5</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -2174,17 +2165,17 @@
         <v>5</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -2192,17 +2183,19 @@
         <v>5</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="2"/>
+        <v>184</v>
+      </c>
       <c r="E57" s="2" t="s">
-        <v>46</v>
+        <v>214</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -2210,19 +2203,19 @@
         <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -2230,19 +2223,19 @@
         <v>5</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -2250,19 +2243,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
@@ -2270,19 +2263,19 @@
         <v>5</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -2290,19 +2283,19 @@
         <v>5</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -2310,19 +2303,19 @@
         <v>5</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -2330,19 +2323,19 @@
         <v>5</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
@@ -2350,19 +2343,19 @@
         <v>5</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>174</v>
+        <v>6</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
@@ -2370,19 +2363,19 @@
         <v>5</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>6</v>
+        <v>174</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
@@ -2390,19 +2383,19 @@
         <v>5</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
@@ -2410,19 +2403,19 @@
         <v>5</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
@@ -2430,19 +2423,19 @@
         <v>5</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
@@ -2450,19 +2443,19 @@
         <v>5</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>3</v>
+        <v>177</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>3</v>
+        <v>177</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -2470,19 +2463,19 @@
         <v>5</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -2490,19 +2483,19 @@
         <v>5</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
@@ -2510,19 +2503,19 @@
         <v>5</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I73" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="K73" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -2530,60 +2523,47 @@
         <v>5</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>6</v>
+        <v>215</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
@@ -2679,7 +2659,7 @@
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="C91" s="3"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
     </row>
@@ -2693,14 +2673,14 @@
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="3"/>
+      <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
+      <c r="C94" s="3"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
     </row>
@@ -2765,14 +2745,14 @@
       <c r="B103" s="2"/>
       <c r="C103" s="3"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
+      <c r="E103" s="4"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="3"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="4"/>
+      <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
@@ -2784,21 +2764,21 @@
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
-      <c r="C106" s="3"/>
+      <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
+      <c r="C107" s="3"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
-      <c r="C108" s="3"/>
+      <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
     </row>
@@ -3719,16 +3699,9 @@
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A240" s="2"/>
-      <c r="B240" s="2"/>
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E240">
-    <sortCondition ref="A36:A240"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E239">
+    <sortCondition ref="A35:A239"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3746,19 +3719,19 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3766,19 +3739,19 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3786,19 +3759,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3806,19 +3779,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3826,19 +3799,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3846,19 +3819,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3866,19 +3839,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3886,19 +3859,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3906,19 +3879,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
